--- a/docs/data/climate_targets_data.xlsx
+++ b/docs/data/climate_targets_data.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My MacBook Pro\docs\atlas_july26\targets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My MacBook Pro\docs\regulations_test\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C05AED4C-D7A8-4F3B-9DBF-00A64367F735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD8F31FB-4472-460F-8FF2-368F9B2ED25B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28635" yWindow="630" windowWidth="26160" windowHeight="12825" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
+    <sheet name="climate_targets_data" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -3008,9 +3008,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8003,7 +8003,7 @@
       <c r="T74" s="3"/>
       <c r="U74" s="3"/>
       <c r="V74" s="3"/>
-      <c r="W74" s="26" t="s">
+      <c r="W74" s="28" t="s">
         <v>162</v>
       </c>
       <c r="X74" s="23"/>
@@ -12286,7 +12286,7 @@
       <c r="T141" s="3"/>
       <c r="U141" s="3"/>
       <c r="V141" s="3"/>
-      <c r="W141" s="26" t="s">
+      <c r="W141" s="28" t="s">
         <v>263</v>
       </c>
       <c r="X141" s="23"/>
@@ -17195,7 +17195,7 @@
       <c r="T221" s="3"/>
       <c r="U221" s="3"/>
       <c r="V221" s="3"/>
-      <c r="W221" s="28" t="s">
+      <c r="W221" s="26" t="s">
         <v>351</v>
       </c>
       <c r="X221" s="23"/>
@@ -17951,7 +17951,7 @@
       <c r="T233" s="3"/>
       <c r="U233" s="3"/>
       <c r="V233" s="3"/>
-      <c r="W233" s="26" t="s">
+      <c r="W233" s="28" t="s">
         <v>364</v>
       </c>
       <c r="X233" s="23"/>
@@ -20743,7 +20743,7 @@
       <c r="Q277" s="3"/>
       <c r="R277" s="3"/>
       <c r="S277" s="3"/>
-      <c r="T277" s="26"/>
+      <c r="T277" s="28"/>
       <c r="U277" s="23"/>
       <c r="V277" s="3"/>
       <c r="W277" s="22" t="s">
@@ -22058,7 +22058,7 @@
       <c r="T298" s="3"/>
       <c r="U298" s="3"/>
       <c r="V298" s="3"/>
-      <c r="W298" s="26" t="s">
+      <c r="W298" s="28" t="s">
         <v>455</v>
       </c>
       <c r="X298" s="23"/>
@@ -30060,7 +30060,7 @@
       <c r="Q423" s="3"/>
       <c r="R423" s="3"/>
       <c r="S423" s="3"/>
-      <c r="T423" s="26"/>
+      <c r="T423" s="28"/>
       <c r="U423" s="23"/>
       <c r="V423" s="3"/>
       <c r="W423" s="24" t="s">
@@ -30119,7 +30119,7 @@
       <c r="Q424" s="3"/>
       <c r="R424" s="3"/>
       <c r="S424" s="3"/>
-      <c r="T424" s="26"/>
+      <c r="T424" s="28"/>
       <c r="U424" s="23"/>
       <c r="V424" s="3"/>
       <c r="W424" s="24" t="s">
@@ -30239,7 +30239,7 @@
       <c r="Q426" s="3"/>
       <c r="R426" s="3"/>
       <c r="S426" s="3"/>
-      <c r="T426" s="26"/>
+      <c r="T426" s="28"/>
       <c r="U426" s="23"/>
       <c r="V426" s="3"/>
       <c r="W426" s="22" t="s">
@@ -30298,7 +30298,7 @@
       <c r="Q427" s="3"/>
       <c r="R427" s="3"/>
       <c r="S427" s="3"/>
-      <c r="T427" s="26"/>
+      <c r="T427" s="28"/>
       <c r="U427" s="23"/>
       <c r="V427" s="3"/>
       <c r="W427" s="22" t="s">
@@ -33250,7 +33250,7 @@
       <c r="T474" s="10"/>
       <c r="U474" s="10"/>
       <c r="V474" s="10"/>
-      <c r="W474" s="28" t="s">
+      <c r="W474" s="26" t="s">
         <v>86</v>
       </c>
       <c r="X474" s="23"/>
@@ -33606,7 +33606,7 @@
       <c r="T480" s="3"/>
       <c r="U480" s="3"/>
       <c r="V480" s="3"/>
-      <c r="W480" s="26" t="s">
+      <c r="W480" s="28" t="s">
         <v>736</v>
       </c>
       <c r="X480" s="23"/>
@@ -42435,18 +42435,595 @@
     </row>
   </sheetData>
   <mergeCells count="637">
-    <mergeCell ref="W39:X39"/>
-    <mergeCell ref="W481:X481"/>
-    <mergeCell ref="W166:X166"/>
-    <mergeCell ref="W337:X337"/>
-    <mergeCell ref="W464:X464"/>
-    <mergeCell ref="W402:X402"/>
-    <mergeCell ref="W573:X573"/>
-    <mergeCell ref="W352:X352"/>
-    <mergeCell ref="W103:X103"/>
-    <mergeCell ref="W401:X401"/>
-    <mergeCell ref="W339:X339"/>
-    <mergeCell ref="W466:X466"/>
+    <mergeCell ref="W128:X128"/>
+    <mergeCell ref="W426:X426"/>
+    <mergeCell ref="W255:X255"/>
+    <mergeCell ref="W364:X364"/>
+    <mergeCell ref="W497:X497"/>
+    <mergeCell ref="W413:X413"/>
+    <mergeCell ref="W65:X65"/>
+    <mergeCell ref="W192:X192"/>
+    <mergeCell ref="W428:X428"/>
+    <mergeCell ref="W355:X355"/>
+    <mergeCell ref="W415:X415"/>
+    <mergeCell ref="W277:X277"/>
+    <mergeCell ref="W404:X404"/>
+    <mergeCell ref="W586:X586"/>
+    <mergeCell ref="W713:X713"/>
+    <mergeCell ref="W129:X129"/>
+    <mergeCell ref="W63:X63"/>
+    <mergeCell ref="W123:X123"/>
+    <mergeCell ref="W365:X365"/>
+    <mergeCell ref="W50:X50"/>
+    <mergeCell ref="W492:X492"/>
+    <mergeCell ref="W286:X286"/>
+    <mergeCell ref="W479:X479"/>
+    <mergeCell ref="W650:X650"/>
+    <mergeCell ref="W87:X87"/>
+    <mergeCell ref="W77:X77"/>
+    <mergeCell ref="W440:X440"/>
+    <mergeCell ref="W611:X611"/>
+    <mergeCell ref="W240:X240"/>
+    <mergeCell ref="W669:X669"/>
+    <mergeCell ref="W377:X377"/>
+    <mergeCell ref="W548:X548"/>
+    <mergeCell ref="W206:X206"/>
+    <mergeCell ref="W635:X635"/>
+    <mergeCell ref="W695:X695"/>
+    <mergeCell ref="W629:X629"/>
+    <mergeCell ref="W708:X708"/>
+    <mergeCell ref="W715:X715"/>
+    <mergeCell ref="W131:X131"/>
+    <mergeCell ref="W690:X690"/>
+    <mergeCell ref="W494:X494"/>
+    <mergeCell ref="W350:X350"/>
+    <mergeCell ref="W410:X410"/>
+    <mergeCell ref="W456:X456"/>
+    <mergeCell ref="W568:X568"/>
+    <mergeCell ref="W731:X731"/>
+    <mergeCell ref="W722:X722"/>
+    <mergeCell ref="W685:X685"/>
+    <mergeCell ref="W427:X427"/>
+    <mergeCell ref="W451:X451"/>
+    <mergeCell ref="W245:X245"/>
+    <mergeCell ref="W516:X516"/>
+    <mergeCell ref="W687:X687"/>
+    <mergeCell ref="W614:X614"/>
+    <mergeCell ref="W193:X193"/>
+    <mergeCell ref="W168:X168"/>
+    <mergeCell ref="W698:X698"/>
+    <mergeCell ref="W148:X148"/>
+    <mergeCell ref="W204:X204"/>
+    <mergeCell ref="W179:X179"/>
+    <mergeCell ref="W446:X446"/>
+    <mergeCell ref="W14:X14"/>
+    <mergeCell ref="W318:X318"/>
+    <mergeCell ref="W312:X312"/>
+    <mergeCell ref="W579:X579"/>
+    <mergeCell ref="W668:X668"/>
+    <mergeCell ref="W78:X78"/>
+    <mergeCell ref="W376:X376"/>
+    <mergeCell ref="W643:X643"/>
+    <mergeCell ref="W205:X205"/>
+    <mergeCell ref="W314:X314"/>
+    <mergeCell ref="W124:X124"/>
+    <mergeCell ref="W645:X645"/>
+    <mergeCell ref="W55:X55"/>
+    <mergeCell ref="W608:X608"/>
+    <mergeCell ref="W595:X595"/>
+    <mergeCell ref="W76:X76"/>
+    <mergeCell ref="W659:X659"/>
+    <mergeCell ref="W29:X29"/>
+    <mergeCell ref="W23:X23"/>
+    <mergeCell ref="W216:X216"/>
+    <mergeCell ref="W514:X514"/>
+    <mergeCell ref="W452:X452"/>
+    <mergeCell ref="W550:X550"/>
+    <mergeCell ref="W160:X160"/>
+    <mergeCell ref="T367:U367"/>
+    <mergeCell ref="W118:X118"/>
+    <mergeCell ref="W482:X482"/>
+    <mergeCell ref="W167:X167"/>
+    <mergeCell ref="W142:X142"/>
+    <mergeCell ref="W80:X80"/>
+    <mergeCell ref="W403:X403"/>
+    <mergeCell ref="W378:X378"/>
+    <mergeCell ref="W574:X574"/>
+    <mergeCell ref="T277:U277"/>
+    <mergeCell ref="W182:X182"/>
+    <mergeCell ref="W169:X169"/>
+    <mergeCell ref="W434:X434"/>
+    <mergeCell ref="W372:X372"/>
+    <mergeCell ref="W310:X310"/>
+    <mergeCell ref="W163:X163"/>
+    <mergeCell ref="W138:X138"/>
+    <mergeCell ref="W309:X309"/>
+    <mergeCell ref="W374:X374"/>
+    <mergeCell ref="W361:X361"/>
+    <mergeCell ref="W140:X140"/>
+    <mergeCell ref="W311:X311"/>
+    <mergeCell ref="W229:X229"/>
+    <mergeCell ref="W387:X387"/>
+    <mergeCell ref="W7:X7"/>
+    <mergeCell ref="W200:X200"/>
+    <mergeCell ref="U734:V734"/>
+    <mergeCell ref="W292:X292"/>
+    <mergeCell ref="W563:X563"/>
+    <mergeCell ref="W721:X721"/>
+    <mergeCell ref="W71:X71"/>
+    <mergeCell ref="W429:X429"/>
+    <mergeCell ref="W58:X58"/>
+    <mergeCell ref="W500:X500"/>
+    <mergeCell ref="W258:X258"/>
+    <mergeCell ref="W294:X294"/>
+    <mergeCell ref="W592:X592"/>
+    <mergeCell ref="W8:X8"/>
+    <mergeCell ref="W684:X684"/>
+    <mergeCell ref="W711:X711"/>
+    <mergeCell ref="W686:X686"/>
+    <mergeCell ref="W539:X539"/>
+    <mergeCell ref="W333:X333"/>
+    <mergeCell ref="W10:X10"/>
+    <mergeCell ref="W501:X501"/>
+    <mergeCell ref="W99:X99"/>
+    <mergeCell ref="W664:X664"/>
+    <mergeCell ref="W74:X74"/>
+    <mergeCell ref="W2:X2"/>
+    <mergeCell ref="W366:X366"/>
+    <mergeCell ref="W437:X437"/>
+    <mergeCell ref="W371:X371"/>
+    <mergeCell ref="W431:X431"/>
+    <mergeCell ref="W60:X60"/>
+    <mergeCell ref="W502:X502"/>
+    <mergeCell ref="W729:X729"/>
+    <mergeCell ref="W358:X358"/>
+    <mergeCell ref="W231:X231"/>
+    <mergeCell ref="W287:X287"/>
+    <mergeCell ref="W656:X656"/>
+    <mergeCell ref="W594:X594"/>
+    <mergeCell ref="W716:X716"/>
+    <mergeCell ref="W53:X53"/>
+    <mergeCell ref="W495:X495"/>
+    <mergeCell ref="W422:X422"/>
+    <mergeCell ref="W593:X593"/>
+    <mergeCell ref="W360:X360"/>
+    <mergeCell ref="W289:X289"/>
+    <mergeCell ref="W658:X658"/>
+    <mergeCell ref="W68:X68"/>
+    <mergeCell ref="W239:X239"/>
+    <mergeCell ref="W84:X84"/>
+    <mergeCell ref="W5:X5"/>
+    <mergeCell ref="W447:X447"/>
+    <mergeCell ref="W618:X618"/>
+    <mergeCell ref="W384:X384"/>
+    <mergeCell ref="W449:X449"/>
+    <mergeCell ref="W150:X150"/>
+    <mergeCell ref="W144:X144"/>
+    <mergeCell ref="W411:X411"/>
+    <mergeCell ref="W386:X386"/>
+    <mergeCell ref="W442:X442"/>
+    <mergeCell ref="W513:X513"/>
+    <mergeCell ref="W21:X21"/>
+    <mergeCell ref="W152:X152"/>
+    <mergeCell ref="W208:X208"/>
+    <mergeCell ref="W450:X450"/>
+    <mergeCell ref="W244:X244"/>
+    <mergeCell ref="W425:X425"/>
+    <mergeCell ref="W219:X219"/>
+    <mergeCell ref="W210:X210"/>
+    <mergeCell ref="W477:X477"/>
+    <mergeCell ref="W283:X283"/>
+    <mergeCell ref="W519:X519"/>
+    <mergeCell ref="W589:X589"/>
+    <mergeCell ref="W241:X241"/>
+    <mergeCell ref="U733:V733"/>
+    <mergeCell ref="W24:X24"/>
+    <mergeCell ref="W89:X89"/>
+    <mergeCell ref="W260:X260"/>
+    <mergeCell ref="W453:X453"/>
+    <mergeCell ref="W545:X545"/>
+    <mergeCell ref="W26:X26"/>
+    <mergeCell ref="W324:X324"/>
+    <mergeCell ref="W113:X113"/>
+    <mergeCell ref="W380:X380"/>
+    <mergeCell ref="W184:X184"/>
+    <mergeCell ref="W616:X616"/>
+    <mergeCell ref="W100:X100"/>
+    <mergeCell ref="W165:X165"/>
+    <mergeCell ref="W336:X336"/>
+    <mergeCell ref="W634:X634"/>
+    <mergeCell ref="W705:X705"/>
+    <mergeCell ref="T660:U660"/>
+    <mergeCell ref="W115:X115"/>
+    <mergeCell ref="W382:X382"/>
+    <mergeCell ref="U680:V680"/>
+    <mergeCell ref="W42:X42"/>
+    <mergeCell ref="W400:X400"/>
+    <mergeCell ref="W471:X471"/>
+    <mergeCell ref="W37:X37"/>
+    <mergeCell ref="W304:X304"/>
+    <mergeCell ref="W602:X602"/>
+    <mergeCell ref="W540:X540"/>
+    <mergeCell ref="W143:X143"/>
+    <mergeCell ref="W329:X329"/>
+    <mergeCell ref="W627:X627"/>
+    <mergeCell ref="W230:X230"/>
+    <mergeCell ref="W95:X95"/>
+    <mergeCell ref="W537:X537"/>
+    <mergeCell ref="W266:X266"/>
+    <mergeCell ref="W393:X393"/>
+    <mergeCell ref="W564:X564"/>
+    <mergeCell ref="W331:X331"/>
+    <mergeCell ref="W232:X232"/>
+    <mergeCell ref="W104:X104"/>
+    <mergeCell ref="W340:X340"/>
+    <mergeCell ref="W79:X79"/>
+    <mergeCell ref="W54:X54"/>
+    <mergeCell ref="W321:X321"/>
+    <mergeCell ref="W508:X508"/>
+    <mergeCell ref="W613:X613"/>
+    <mergeCell ref="W41:X41"/>
+    <mergeCell ref="W106:X106"/>
+    <mergeCell ref="W32:X32"/>
+    <mergeCell ref="W159:X159"/>
+    <mergeCell ref="W330:X330"/>
+    <mergeCell ref="W97:X97"/>
+    <mergeCell ref="W153:X153"/>
+    <mergeCell ref="W395:X395"/>
+    <mergeCell ref="W517:X517"/>
+    <mergeCell ref="W693:X693"/>
+    <mergeCell ref="W553:X553"/>
+    <mergeCell ref="W96:X96"/>
+    <mergeCell ref="W90:X90"/>
+    <mergeCell ref="W532:X532"/>
+    <mergeCell ref="W503:X503"/>
+    <mergeCell ref="W161:X161"/>
+    <mergeCell ref="W261:X261"/>
+    <mergeCell ref="W459:X459"/>
+    <mergeCell ref="W630:X630"/>
+    <mergeCell ref="W332:X332"/>
+    <mergeCell ref="W617:X617"/>
+    <mergeCell ref="W256:X256"/>
+    <mergeCell ref="W554:X554"/>
+    <mergeCell ref="W47:X47"/>
+    <mergeCell ref="W541:X541"/>
+    <mergeCell ref="W345:X345"/>
+    <mergeCell ref="W27:X27"/>
+    <mergeCell ref="W421:X421"/>
+    <mergeCell ref="W250:X250"/>
+    <mergeCell ref="W44:X44"/>
+    <mergeCell ref="W408:X408"/>
+    <mergeCell ref="W535:X535"/>
+    <mergeCell ref="W706:X706"/>
+    <mergeCell ref="W116:X116"/>
+    <mergeCell ref="W187:X187"/>
+    <mergeCell ref="W681:X681"/>
+    <mergeCell ref="W485:X485"/>
+    <mergeCell ref="W619:X619"/>
+    <mergeCell ref="W423:X423"/>
+    <mergeCell ref="W174:X174"/>
+    <mergeCell ref="W108:X108"/>
+    <mergeCell ref="W472:X472"/>
+    <mergeCell ref="W254:X254"/>
+    <mergeCell ref="W189:X189"/>
+    <mergeCell ref="W683:X683"/>
+    <mergeCell ref="W487:X487"/>
+    <mergeCell ref="W45:X45"/>
+    <mergeCell ref="W238:X238"/>
+    <mergeCell ref="W343:X343"/>
+    <mergeCell ref="W474:X474"/>
+    <mergeCell ref="W22:X22"/>
+    <mergeCell ref="W263:X263"/>
+    <mergeCell ref="W320:X320"/>
+    <mergeCell ref="W134:X134"/>
+    <mergeCell ref="W572:X572"/>
+    <mergeCell ref="W121:X121"/>
+    <mergeCell ref="W701:X701"/>
+    <mergeCell ref="W111:X111"/>
+    <mergeCell ref="W98:X98"/>
+    <mergeCell ref="W567:X567"/>
+    <mergeCell ref="W225:X225"/>
+    <mergeCell ref="W467:X467"/>
+    <mergeCell ref="W638:X638"/>
+    <mergeCell ref="W461:X461"/>
+    <mergeCell ref="W35:X35"/>
+    <mergeCell ref="W66:X66"/>
+    <mergeCell ref="W109:X109"/>
+    <mergeCell ref="W587:X587"/>
+    <mergeCell ref="W28:X28"/>
+    <mergeCell ref="W246:X246"/>
+    <mergeCell ref="W233:X233"/>
+    <mergeCell ref="W531:X531"/>
+    <mergeCell ref="W469:X469"/>
+    <mergeCell ref="W248:X248"/>
+    <mergeCell ref="W703:X703"/>
+    <mergeCell ref="W175:X175"/>
+    <mergeCell ref="W162:X162"/>
+    <mergeCell ref="W569:X569"/>
+    <mergeCell ref="W525:X525"/>
+    <mergeCell ref="W696:X696"/>
+    <mergeCell ref="T426:U426"/>
+    <mergeCell ref="W177:X177"/>
+    <mergeCell ref="W164:X164"/>
+    <mergeCell ref="W335:X335"/>
+    <mergeCell ref="W462:X462"/>
+    <mergeCell ref="W556:X556"/>
+    <mergeCell ref="W251:X251"/>
+    <mergeCell ref="W493:X493"/>
+    <mergeCell ref="W414:X414"/>
+    <mergeCell ref="W585:X585"/>
+    <mergeCell ref="W188:X188"/>
+    <mergeCell ref="W259:X259"/>
+    <mergeCell ref="W424:X424"/>
+    <mergeCell ref="W253:X253"/>
+    <mergeCell ref="W551:X551"/>
+    <mergeCell ref="W351:X351"/>
+    <mergeCell ref="W180:X180"/>
+    <mergeCell ref="W538:X538"/>
+    <mergeCell ref="W709:X709"/>
+    <mergeCell ref="W59:X59"/>
+    <mergeCell ref="W190:X190"/>
+    <mergeCell ref="W46:X46"/>
+    <mergeCell ref="W488:X488"/>
+    <mergeCell ref="W117:X117"/>
+    <mergeCell ref="W282:X282"/>
+    <mergeCell ref="W724:X724"/>
+    <mergeCell ref="W353:X353"/>
+    <mergeCell ref="W409:X409"/>
+    <mergeCell ref="W651:X651"/>
+    <mergeCell ref="W257:X257"/>
+    <mergeCell ref="W61:X61"/>
+    <mergeCell ref="W48:X48"/>
+    <mergeCell ref="W490:X490"/>
+    <mergeCell ref="W578:X578"/>
+    <mergeCell ref="W626:X626"/>
+    <mergeCell ref="W222:X222"/>
+    <mergeCell ref="W284:X284"/>
+    <mergeCell ref="W520:X520"/>
+    <mergeCell ref="W101:X101"/>
+    <mergeCell ref="W666:X666"/>
+    <mergeCell ref="W628:X628"/>
+    <mergeCell ref="W432:X432"/>
+    <mergeCell ref="T423:U423"/>
+    <mergeCell ref="W346:X346"/>
+    <mergeCell ref="W112:X112"/>
+    <mergeCell ref="W348:X348"/>
+    <mergeCell ref="W727:X727"/>
+    <mergeCell ref="W137:X137"/>
+    <mergeCell ref="W702:X702"/>
+    <mergeCell ref="W640:X640"/>
+    <mergeCell ref="W300:X300"/>
+    <mergeCell ref="W183:X183"/>
+    <mergeCell ref="W201:X201"/>
+    <mergeCell ref="W443:X443"/>
+    <mergeCell ref="W406:X406"/>
+    <mergeCell ref="U679:V679"/>
+    <mergeCell ref="W139:X139"/>
+    <mergeCell ref="W704:X704"/>
+    <mergeCell ref="W560:X560"/>
+    <mergeCell ref="W498:X498"/>
+    <mergeCell ref="W114:X114"/>
+    <mergeCell ref="W185:X185"/>
+    <mergeCell ref="W247:X247"/>
+    <mergeCell ref="W483:X483"/>
+    <mergeCell ref="W203:X203"/>
+    <mergeCell ref="W470:X470"/>
+    <mergeCell ref="W3:X3"/>
+    <mergeCell ref="W243:X243"/>
+    <mergeCell ref="W43:X43"/>
+    <mergeCell ref="W267:X267"/>
+    <mergeCell ref="W130:X130"/>
+    <mergeCell ref="W67:X67"/>
+    <mergeCell ref="W132:X132"/>
+    <mergeCell ref="W496:X496"/>
+    <mergeCell ref="W430:X430"/>
+    <mergeCell ref="W119:X119"/>
+    <mergeCell ref="W11:X11"/>
+    <mergeCell ref="W19:X19"/>
+    <mergeCell ref="W317:X317"/>
+    <mergeCell ref="W357:X357"/>
+    <mergeCell ref="W12:X12"/>
+    <mergeCell ref="W72:X72"/>
+    <mergeCell ref="W9:X9"/>
+    <mergeCell ref="W38:X38"/>
+    <mergeCell ref="W13:X13"/>
+    <mergeCell ref="W93:X93"/>
+    <mergeCell ref="W86:X86"/>
+    <mergeCell ref="W157:X157"/>
+    <mergeCell ref="W455:X455"/>
+    <mergeCell ref="W151:X151"/>
+    <mergeCell ref="W732:X732"/>
+    <mergeCell ref="W290:X290"/>
+    <mergeCell ref="W417:X417"/>
+    <mergeCell ref="W588:X588"/>
+    <mergeCell ref="W653:X653"/>
+    <mergeCell ref="W69:X69"/>
+    <mergeCell ref="W367:X367"/>
+    <mergeCell ref="W354:X354"/>
+    <mergeCell ref="W652:X652"/>
+    <mergeCell ref="W419:X419"/>
+    <mergeCell ref="W590:X590"/>
+    <mergeCell ref="W717:X717"/>
+    <mergeCell ref="W133:X133"/>
+    <mergeCell ref="W127:X127"/>
+    <mergeCell ref="W298:X298"/>
+    <mergeCell ref="W369:X369"/>
+    <mergeCell ref="W667:X667"/>
+    <mergeCell ref="W418:X418"/>
+    <mergeCell ref="W285:X285"/>
+    <mergeCell ref="W356:X356"/>
+    <mergeCell ref="W527:X527"/>
+    <mergeCell ref="W654:X654"/>
+    <mergeCell ref="W648:X648"/>
+    <mergeCell ref="W342:X342"/>
+    <mergeCell ref="T658:U658"/>
+    <mergeCell ref="W64:X64"/>
+    <mergeCell ref="W51:X51"/>
+    <mergeCell ref="W16:X16"/>
+    <mergeCell ref="W209:X209"/>
+    <mergeCell ref="W445:X445"/>
+    <mergeCell ref="W301:X301"/>
+    <mergeCell ref="W122:X122"/>
+    <mergeCell ref="W730:X730"/>
+    <mergeCell ref="W18:X18"/>
+    <mergeCell ref="W322:X322"/>
+    <mergeCell ref="W509:X509"/>
+    <mergeCell ref="W303:X303"/>
+    <mergeCell ref="W186:X186"/>
+    <mergeCell ref="W601:X601"/>
+    <mergeCell ref="W484:X484"/>
+    <mergeCell ref="W17:X17"/>
+    <mergeCell ref="W288:X288"/>
+    <mergeCell ref="W82:X82"/>
+    <mergeCell ref="W576:X576"/>
+    <mergeCell ref="W707:X707"/>
+    <mergeCell ref="W511:X511"/>
+    <mergeCell ref="W603:X603"/>
+    <mergeCell ref="W486:X486"/>
+    <mergeCell ref="T427:U427"/>
+    <mergeCell ref="W515:X515"/>
+    <mergeCell ref="W344:X344"/>
+    <mergeCell ref="W158:X158"/>
+    <mergeCell ref="W110:X110"/>
+    <mergeCell ref="W723:X723"/>
+    <mergeCell ref="W644:X644"/>
+    <mergeCell ref="W375:X375"/>
+    <mergeCell ref="W489:X489"/>
+    <mergeCell ref="T424:U424"/>
+    <mergeCell ref="W505:X505"/>
+    <mergeCell ref="W480:X480"/>
+    <mergeCell ref="W299:X299"/>
+    <mergeCell ref="W597:X597"/>
+    <mergeCell ref="W612:X612"/>
+    <mergeCell ref="W228:X228"/>
+    <mergeCell ref="W155:X155"/>
+    <mergeCell ref="W264:X264"/>
+    <mergeCell ref="W562:X562"/>
+    <mergeCell ref="W220:X220"/>
+    <mergeCell ref="W518:X518"/>
+    <mergeCell ref="W689:X689"/>
+    <mergeCell ref="W676:X676"/>
+    <mergeCell ref="W170:X170"/>
+    <mergeCell ref="W725:X725"/>
+    <mergeCell ref="W141:X141"/>
+    <mergeCell ref="W368:X368"/>
+    <mergeCell ref="W439:X439"/>
+    <mergeCell ref="W135:X135"/>
+    <mergeCell ref="W433:X433"/>
+    <mergeCell ref="W504:X504"/>
+    <mergeCell ref="W420:X420"/>
+    <mergeCell ref="W591:X591"/>
+    <mergeCell ref="W662:X662"/>
+    <mergeCell ref="W718:X718"/>
+    <mergeCell ref="W224:X224"/>
+    <mergeCell ref="W370:X370"/>
+    <mergeCell ref="W297:X297"/>
+    <mergeCell ref="W435:X435"/>
+    <mergeCell ref="W506:X506"/>
+    <mergeCell ref="W291:X291"/>
+    <mergeCell ref="W655:X655"/>
+    <mergeCell ref="W149:X149"/>
+    <mergeCell ref="W714:X714"/>
+    <mergeCell ref="W385:X385"/>
+    <mergeCell ref="W441:X441"/>
+    <mergeCell ref="W637:X637"/>
+    <mergeCell ref="W207:X207"/>
+    <mergeCell ref="W726:X726"/>
+    <mergeCell ref="T659:U659"/>
+    <mergeCell ref="W136:X136"/>
+    <mergeCell ref="W70:X70"/>
+    <mergeCell ref="W499:X499"/>
+    <mergeCell ref="W657:X657"/>
+    <mergeCell ref="T661:U661"/>
+    <mergeCell ref="W88:X88"/>
+    <mergeCell ref="W688:X688"/>
+    <mergeCell ref="W146:X146"/>
+    <mergeCell ref="W388:X388"/>
+    <mergeCell ref="W510:X510"/>
+    <mergeCell ref="W448:X448"/>
+    <mergeCell ref="W559:X559"/>
+    <mergeCell ref="W546:X546"/>
+    <mergeCell ref="W227:X227"/>
+    <mergeCell ref="W83:X83"/>
+    <mergeCell ref="W154:X154"/>
+    <mergeCell ref="W319:X319"/>
+    <mergeCell ref="W512:X512"/>
+    <mergeCell ref="W561:X561"/>
+    <mergeCell ref="W604:X604"/>
+    <mergeCell ref="W85:X85"/>
+    <mergeCell ref="W383:X383"/>
+    <mergeCell ref="W728:X728"/>
+    <mergeCell ref="W249:X249"/>
+    <mergeCell ref="W4:X4"/>
+    <mergeCell ref="W436:X436"/>
+    <mergeCell ref="W507:X507"/>
+    <mergeCell ref="W40:X40"/>
+    <mergeCell ref="W363:X363"/>
+    <mergeCell ref="W534:X534"/>
+    <mergeCell ref="W605:X605"/>
+    <mergeCell ref="W338:X338"/>
+    <mergeCell ref="W15:X15"/>
+    <mergeCell ref="W313:X313"/>
+    <mergeCell ref="W373:X373"/>
+    <mergeCell ref="W202:X202"/>
+    <mergeCell ref="W444:X444"/>
+    <mergeCell ref="W549:X549"/>
+    <mergeCell ref="W536:X536"/>
+    <mergeCell ref="W663:X663"/>
+    <mergeCell ref="W302:X302"/>
+    <mergeCell ref="W91:X91"/>
+    <mergeCell ref="W389:X389"/>
+    <mergeCell ref="W460:X460"/>
+    <mergeCell ref="W156:X156"/>
+    <mergeCell ref="W454:X454"/>
+    <mergeCell ref="W639:X639"/>
+    <mergeCell ref="W577:X577"/>
+    <mergeCell ref="W145:X145"/>
+    <mergeCell ref="W381:X381"/>
+    <mergeCell ref="W552:X552"/>
+    <mergeCell ref="W226:X226"/>
+    <mergeCell ref="W147:X147"/>
+    <mergeCell ref="W526:X526"/>
+    <mergeCell ref="W697:X697"/>
+    <mergeCell ref="W234:X234"/>
+    <mergeCell ref="W570:X570"/>
+    <mergeCell ref="W692:X692"/>
+    <mergeCell ref="W694:X694"/>
+    <mergeCell ref="W646:X646"/>
+    <mergeCell ref="W491:X491"/>
+    <mergeCell ref="W547:X547"/>
+    <mergeCell ref="W176:X176"/>
+    <mergeCell ref="W347:X347"/>
+    <mergeCell ref="W412:X412"/>
+    <mergeCell ref="W575:X575"/>
+    <mergeCell ref="W252:X252"/>
+    <mergeCell ref="W379:X379"/>
+    <mergeCell ref="W323:X323"/>
+    <mergeCell ref="W615:X615"/>
+    <mergeCell ref="W647:X647"/>
+    <mergeCell ref="W641:X641"/>
+    <mergeCell ref="W34:X34"/>
+    <mergeCell ref="W172:X172"/>
+    <mergeCell ref="W392:X392"/>
+    <mergeCell ref="W25:X25"/>
+    <mergeCell ref="W463:X463"/>
+    <mergeCell ref="W270:X270"/>
+    <mergeCell ref="W221:X221"/>
+    <mergeCell ref="W457:X457"/>
+    <mergeCell ref="W555:X555"/>
+    <mergeCell ref="W359:X359"/>
+    <mergeCell ref="W171:X171"/>
+    <mergeCell ref="W36:X36"/>
+    <mergeCell ref="W92:X92"/>
+    <mergeCell ref="W30:X30"/>
+    <mergeCell ref="W334:X334"/>
+    <mergeCell ref="W394:X394"/>
+    <mergeCell ref="W223:X223"/>
+    <mergeCell ref="W465:X465"/>
+    <mergeCell ref="W173:X173"/>
+    <mergeCell ref="W94:X94"/>
+    <mergeCell ref="W265:X265"/>
+    <mergeCell ref="W31:X31"/>
     <mergeCell ref="W712:X712"/>
     <mergeCell ref="W293:X293"/>
     <mergeCell ref="W49:X49"/>
@@ -42471,607 +43048,30 @@
     <mergeCell ref="W120:X120"/>
     <mergeCell ref="W191:X191"/>
     <mergeCell ref="W107:X107"/>
+    <mergeCell ref="W39:X39"/>
+    <mergeCell ref="W481:X481"/>
+    <mergeCell ref="W166:X166"/>
+    <mergeCell ref="W337:X337"/>
+    <mergeCell ref="W464:X464"/>
+    <mergeCell ref="W402:X402"/>
+    <mergeCell ref="W573:X573"/>
+    <mergeCell ref="W352:X352"/>
+    <mergeCell ref="W103:X103"/>
+    <mergeCell ref="W401:X401"/>
+    <mergeCell ref="W339:X339"/>
+    <mergeCell ref="W466:X466"/>
     <mergeCell ref="W178:X178"/>
     <mergeCell ref="W405:X405"/>
     <mergeCell ref="W349:X349"/>
     <mergeCell ref="W476:X476"/>
-    <mergeCell ref="W647:X647"/>
-    <mergeCell ref="W641:X641"/>
-    <mergeCell ref="W34:X34"/>
-    <mergeCell ref="W172:X172"/>
-    <mergeCell ref="W392:X392"/>
-    <mergeCell ref="W25:X25"/>
-    <mergeCell ref="W463:X463"/>
-    <mergeCell ref="W270:X270"/>
-    <mergeCell ref="W221:X221"/>
-    <mergeCell ref="W457:X457"/>
-    <mergeCell ref="W555:X555"/>
-    <mergeCell ref="W359:X359"/>
-    <mergeCell ref="W171:X171"/>
-    <mergeCell ref="W36:X36"/>
-    <mergeCell ref="W92:X92"/>
-    <mergeCell ref="W30:X30"/>
-    <mergeCell ref="W334:X334"/>
-    <mergeCell ref="W394:X394"/>
-    <mergeCell ref="W223:X223"/>
-    <mergeCell ref="W465:X465"/>
-    <mergeCell ref="W173:X173"/>
-    <mergeCell ref="W94:X94"/>
-    <mergeCell ref="W265:X265"/>
-    <mergeCell ref="W31:X31"/>
     <mergeCell ref="W473:X473"/>
     <mergeCell ref="W475:X475"/>
-    <mergeCell ref="W639:X639"/>
-    <mergeCell ref="W577:X577"/>
-    <mergeCell ref="W145:X145"/>
-    <mergeCell ref="W381:X381"/>
-    <mergeCell ref="W552:X552"/>
-    <mergeCell ref="W226:X226"/>
-    <mergeCell ref="W147:X147"/>
-    <mergeCell ref="W526:X526"/>
-    <mergeCell ref="W697:X697"/>
-    <mergeCell ref="W234:X234"/>
-    <mergeCell ref="W570:X570"/>
-    <mergeCell ref="W692:X692"/>
-    <mergeCell ref="W694:X694"/>
-    <mergeCell ref="W646:X646"/>
-    <mergeCell ref="W491:X491"/>
-    <mergeCell ref="W547:X547"/>
-    <mergeCell ref="W176:X176"/>
-    <mergeCell ref="W347:X347"/>
-    <mergeCell ref="W412:X412"/>
-    <mergeCell ref="W575:X575"/>
     <mergeCell ref="W81:X81"/>
     <mergeCell ref="W56:X56"/>
-    <mergeCell ref="W252:X252"/>
-    <mergeCell ref="W379:X379"/>
-    <mergeCell ref="W323:X323"/>
     <mergeCell ref="W105:X105"/>
-    <mergeCell ref="W615:X615"/>
     <mergeCell ref="W341:X341"/>
     <mergeCell ref="W468:X468"/>
     <mergeCell ref="W57:X57"/>
-    <mergeCell ref="W728:X728"/>
-    <mergeCell ref="W249:X249"/>
-    <mergeCell ref="W4:X4"/>
-    <mergeCell ref="W436:X436"/>
-    <mergeCell ref="W507:X507"/>
-    <mergeCell ref="W40:X40"/>
-    <mergeCell ref="W363:X363"/>
-    <mergeCell ref="W534:X534"/>
-    <mergeCell ref="W605:X605"/>
-    <mergeCell ref="W338:X338"/>
-    <mergeCell ref="W15:X15"/>
-    <mergeCell ref="W313:X313"/>
-    <mergeCell ref="W373:X373"/>
-    <mergeCell ref="W202:X202"/>
-    <mergeCell ref="W444:X444"/>
-    <mergeCell ref="W549:X549"/>
-    <mergeCell ref="W536:X536"/>
-    <mergeCell ref="W663:X663"/>
-    <mergeCell ref="W302:X302"/>
-    <mergeCell ref="W91:X91"/>
-    <mergeCell ref="W389:X389"/>
-    <mergeCell ref="W460:X460"/>
-    <mergeCell ref="W156:X156"/>
-    <mergeCell ref="W454:X454"/>
-    <mergeCell ref="W726:X726"/>
-    <mergeCell ref="T659:U659"/>
-    <mergeCell ref="W136:X136"/>
-    <mergeCell ref="W70:X70"/>
-    <mergeCell ref="W499:X499"/>
-    <mergeCell ref="W657:X657"/>
-    <mergeCell ref="T661:U661"/>
-    <mergeCell ref="W88:X88"/>
-    <mergeCell ref="W688:X688"/>
-    <mergeCell ref="W146:X146"/>
-    <mergeCell ref="W388:X388"/>
-    <mergeCell ref="W510:X510"/>
-    <mergeCell ref="W448:X448"/>
-    <mergeCell ref="W559:X559"/>
-    <mergeCell ref="W546:X546"/>
-    <mergeCell ref="W227:X227"/>
-    <mergeCell ref="W83:X83"/>
-    <mergeCell ref="W154:X154"/>
-    <mergeCell ref="W319:X319"/>
-    <mergeCell ref="W512:X512"/>
-    <mergeCell ref="W561:X561"/>
-    <mergeCell ref="W604:X604"/>
-    <mergeCell ref="W85:X85"/>
-    <mergeCell ref="W383:X383"/>
-    <mergeCell ref="W725:X725"/>
-    <mergeCell ref="W141:X141"/>
-    <mergeCell ref="W368:X368"/>
-    <mergeCell ref="W439:X439"/>
-    <mergeCell ref="W135:X135"/>
-    <mergeCell ref="W433:X433"/>
-    <mergeCell ref="W504:X504"/>
-    <mergeCell ref="W420:X420"/>
-    <mergeCell ref="W591:X591"/>
-    <mergeCell ref="W662:X662"/>
-    <mergeCell ref="W718:X718"/>
-    <mergeCell ref="W224:X224"/>
-    <mergeCell ref="W370:X370"/>
-    <mergeCell ref="W297:X297"/>
-    <mergeCell ref="W435:X435"/>
-    <mergeCell ref="W506:X506"/>
-    <mergeCell ref="W291:X291"/>
-    <mergeCell ref="W655:X655"/>
-    <mergeCell ref="W149:X149"/>
-    <mergeCell ref="W714:X714"/>
-    <mergeCell ref="W385:X385"/>
-    <mergeCell ref="W441:X441"/>
-    <mergeCell ref="W637:X637"/>
-    <mergeCell ref="W207:X207"/>
-    <mergeCell ref="T427:U427"/>
-    <mergeCell ref="W515:X515"/>
-    <mergeCell ref="W344:X344"/>
-    <mergeCell ref="W158:X158"/>
-    <mergeCell ref="W110:X110"/>
-    <mergeCell ref="W723:X723"/>
-    <mergeCell ref="W644:X644"/>
-    <mergeCell ref="W375:X375"/>
-    <mergeCell ref="W489:X489"/>
-    <mergeCell ref="T424:U424"/>
-    <mergeCell ref="W505:X505"/>
-    <mergeCell ref="W480:X480"/>
-    <mergeCell ref="W299:X299"/>
-    <mergeCell ref="W597:X597"/>
-    <mergeCell ref="W612:X612"/>
-    <mergeCell ref="W228:X228"/>
-    <mergeCell ref="W155:X155"/>
-    <mergeCell ref="W264:X264"/>
-    <mergeCell ref="W562:X562"/>
-    <mergeCell ref="W220:X220"/>
-    <mergeCell ref="W518:X518"/>
-    <mergeCell ref="W689:X689"/>
-    <mergeCell ref="W676:X676"/>
-    <mergeCell ref="W170:X170"/>
-    <mergeCell ref="T658:U658"/>
-    <mergeCell ref="W64:X64"/>
-    <mergeCell ref="W51:X51"/>
-    <mergeCell ref="W16:X16"/>
-    <mergeCell ref="W209:X209"/>
-    <mergeCell ref="W445:X445"/>
-    <mergeCell ref="W301:X301"/>
-    <mergeCell ref="W122:X122"/>
-    <mergeCell ref="W730:X730"/>
-    <mergeCell ref="W18:X18"/>
-    <mergeCell ref="W322:X322"/>
-    <mergeCell ref="W509:X509"/>
-    <mergeCell ref="W303:X303"/>
-    <mergeCell ref="W186:X186"/>
-    <mergeCell ref="W601:X601"/>
-    <mergeCell ref="W484:X484"/>
-    <mergeCell ref="W17:X17"/>
-    <mergeCell ref="W288:X288"/>
-    <mergeCell ref="W82:X82"/>
-    <mergeCell ref="W576:X576"/>
-    <mergeCell ref="W707:X707"/>
-    <mergeCell ref="W511:X511"/>
-    <mergeCell ref="W603:X603"/>
-    <mergeCell ref="W486:X486"/>
-    <mergeCell ref="W732:X732"/>
-    <mergeCell ref="W290:X290"/>
-    <mergeCell ref="W417:X417"/>
-    <mergeCell ref="W588:X588"/>
-    <mergeCell ref="W653:X653"/>
-    <mergeCell ref="W69:X69"/>
-    <mergeCell ref="W367:X367"/>
-    <mergeCell ref="W354:X354"/>
-    <mergeCell ref="W652:X652"/>
-    <mergeCell ref="W419:X419"/>
-    <mergeCell ref="W590:X590"/>
-    <mergeCell ref="W717:X717"/>
-    <mergeCell ref="W133:X133"/>
-    <mergeCell ref="W127:X127"/>
-    <mergeCell ref="W298:X298"/>
-    <mergeCell ref="W369:X369"/>
-    <mergeCell ref="W667:X667"/>
-    <mergeCell ref="W418:X418"/>
-    <mergeCell ref="W285:X285"/>
-    <mergeCell ref="W356:X356"/>
-    <mergeCell ref="W527:X527"/>
-    <mergeCell ref="W654:X654"/>
-    <mergeCell ref="W648:X648"/>
-    <mergeCell ref="W342:X342"/>
-    <mergeCell ref="W3:X3"/>
-    <mergeCell ref="W243:X243"/>
-    <mergeCell ref="W43:X43"/>
-    <mergeCell ref="W267:X267"/>
-    <mergeCell ref="W130:X130"/>
-    <mergeCell ref="W67:X67"/>
-    <mergeCell ref="W132:X132"/>
-    <mergeCell ref="W496:X496"/>
-    <mergeCell ref="W430:X430"/>
-    <mergeCell ref="W119:X119"/>
-    <mergeCell ref="W11:X11"/>
-    <mergeCell ref="W19:X19"/>
-    <mergeCell ref="W317:X317"/>
-    <mergeCell ref="W357:X357"/>
-    <mergeCell ref="W12:X12"/>
-    <mergeCell ref="W72:X72"/>
-    <mergeCell ref="W9:X9"/>
-    <mergeCell ref="W38:X38"/>
-    <mergeCell ref="W13:X13"/>
-    <mergeCell ref="W93:X93"/>
-    <mergeCell ref="W86:X86"/>
-    <mergeCell ref="W157:X157"/>
-    <mergeCell ref="W455:X455"/>
-    <mergeCell ref="W151:X151"/>
-    <mergeCell ref="T423:U423"/>
-    <mergeCell ref="W346:X346"/>
-    <mergeCell ref="W112:X112"/>
-    <mergeCell ref="W348:X348"/>
-    <mergeCell ref="W727:X727"/>
-    <mergeCell ref="W137:X137"/>
-    <mergeCell ref="W702:X702"/>
-    <mergeCell ref="W640:X640"/>
-    <mergeCell ref="W300:X300"/>
-    <mergeCell ref="W183:X183"/>
-    <mergeCell ref="W201:X201"/>
-    <mergeCell ref="W443:X443"/>
-    <mergeCell ref="W406:X406"/>
-    <mergeCell ref="U679:V679"/>
-    <mergeCell ref="W139:X139"/>
-    <mergeCell ref="W704:X704"/>
-    <mergeCell ref="W560:X560"/>
-    <mergeCell ref="W498:X498"/>
-    <mergeCell ref="W114:X114"/>
-    <mergeCell ref="W185:X185"/>
-    <mergeCell ref="W247:X247"/>
-    <mergeCell ref="W483:X483"/>
-    <mergeCell ref="W203:X203"/>
-    <mergeCell ref="W470:X470"/>
-    <mergeCell ref="W709:X709"/>
-    <mergeCell ref="W59:X59"/>
-    <mergeCell ref="W190:X190"/>
-    <mergeCell ref="W46:X46"/>
-    <mergeCell ref="W488:X488"/>
-    <mergeCell ref="W117:X117"/>
-    <mergeCell ref="W282:X282"/>
-    <mergeCell ref="W724:X724"/>
-    <mergeCell ref="W353:X353"/>
-    <mergeCell ref="W409:X409"/>
-    <mergeCell ref="W651:X651"/>
-    <mergeCell ref="W257:X257"/>
-    <mergeCell ref="W61:X61"/>
-    <mergeCell ref="W48:X48"/>
-    <mergeCell ref="W490:X490"/>
-    <mergeCell ref="W578:X578"/>
-    <mergeCell ref="W626:X626"/>
-    <mergeCell ref="W222:X222"/>
-    <mergeCell ref="W284:X284"/>
-    <mergeCell ref="W520:X520"/>
-    <mergeCell ref="W101:X101"/>
-    <mergeCell ref="W666:X666"/>
-    <mergeCell ref="W628:X628"/>
-    <mergeCell ref="W432:X432"/>
-    <mergeCell ref="W703:X703"/>
-    <mergeCell ref="W175:X175"/>
-    <mergeCell ref="W162:X162"/>
-    <mergeCell ref="W569:X569"/>
-    <mergeCell ref="W525:X525"/>
-    <mergeCell ref="W696:X696"/>
-    <mergeCell ref="T426:U426"/>
-    <mergeCell ref="W177:X177"/>
-    <mergeCell ref="W164:X164"/>
-    <mergeCell ref="W335:X335"/>
-    <mergeCell ref="W462:X462"/>
-    <mergeCell ref="W556:X556"/>
-    <mergeCell ref="W251:X251"/>
-    <mergeCell ref="W493:X493"/>
-    <mergeCell ref="W414:X414"/>
-    <mergeCell ref="W585:X585"/>
-    <mergeCell ref="W188:X188"/>
-    <mergeCell ref="W259:X259"/>
-    <mergeCell ref="W424:X424"/>
-    <mergeCell ref="W253:X253"/>
-    <mergeCell ref="W551:X551"/>
-    <mergeCell ref="W351:X351"/>
-    <mergeCell ref="W180:X180"/>
-    <mergeCell ref="W538:X538"/>
-    <mergeCell ref="W22:X22"/>
-    <mergeCell ref="W263:X263"/>
-    <mergeCell ref="W320:X320"/>
-    <mergeCell ref="W134:X134"/>
-    <mergeCell ref="W572:X572"/>
-    <mergeCell ref="W121:X121"/>
-    <mergeCell ref="W701:X701"/>
-    <mergeCell ref="W111:X111"/>
-    <mergeCell ref="W98:X98"/>
-    <mergeCell ref="W567:X567"/>
-    <mergeCell ref="W225:X225"/>
-    <mergeCell ref="W467:X467"/>
-    <mergeCell ref="W638:X638"/>
-    <mergeCell ref="W461:X461"/>
-    <mergeCell ref="W35:X35"/>
-    <mergeCell ref="W66:X66"/>
-    <mergeCell ref="W109:X109"/>
-    <mergeCell ref="W587:X587"/>
-    <mergeCell ref="W28:X28"/>
-    <mergeCell ref="W246:X246"/>
-    <mergeCell ref="W233:X233"/>
-    <mergeCell ref="W531:X531"/>
-    <mergeCell ref="W469:X469"/>
-    <mergeCell ref="W248:X248"/>
-    <mergeCell ref="W27:X27"/>
-    <mergeCell ref="W421:X421"/>
-    <mergeCell ref="W250:X250"/>
-    <mergeCell ref="W44:X44"/>
-    <mergeCell ref="W408:X408"/>
-    <mergeCell ref="W535:X535"/>
-    <mergeCell ref="W706:X706"/>
-    <mergeCell ref="W116:X116"/>
-    <mergeCell ref="W187:X187"/>
-    <mergeCell ref="W681:X681"/>
-    <mergeCell ref="W485:X485"/>
-    <mergeCell ref="W619:X619"/>
-    <mergeCell ref="W423:X423"/>
-    <mergeCell ref="W174:X174"/>
-    <mergeCell ref="W108:X108"/>
-    <mergeCell ref="W472:X472"/>
-    <mergeCell ref="W254:X254"/>
-    <mergeCell ref="W189:X189"/>
-    <mergeCell ref="W683:X683"/>
-    <mergeCell ref="W487:X487"/>
-    <mergeCell ref="W45:X45"/>
-    <mergeCell ref="W238:X238"/>
-    <mergeCell ref="W343:X343"/>
-    <mergeCell ref="W474:X474"/>
-    <mergeCell ref="W32:X32"/>
-    <mergeCell ref="W159:X159"/>
-    <mergeCell ref="W330:X330"/>
-    <mergeCell ref="W97:X97"/>
-    <mergeCell ref="W153:X153"/>
-    <mergeCell ref="W395:X395"/>
-    <mergeCell ref="W517:X517"/>
-    <mergeCell ref="W693:X693"/>
-    <mergeCell ref="W553:X553"/>
-    <mergeCell ref="W96:X96"/>
-    <mergeCell ref="W90:X90"/>
-    <mergeCell ref="W532:X532"/>
-    <mergeCell ref="W503:X503"/>
-    <mergeCell ref="W161:X161"/>
-    <mergeCell ref="W261:X261"/>
-    <mergeCell ref="W459:X459"/>
-    <mergeCell ref="W630:X630"/>
-    <mergeCell ref="W332:X332"/>
-    <mergeCell ref="W617:X617"/>
-    <mergeCell ref="W256:X256"/>
-    <mergeCell ref="W554:X554"/>
-    <mergeCell ref="W47:X47"/>
-    <mergeCell ref="W541:X541"/>
-    <mergeCell ref="W345:X345"/>
-    <mergeCell ref="W37:X37"/>
-    <mergeCell ref="W304:X304"/>
-    <mergeCell ref="W602:X602"/>
-    <mergeCell ref="W540:X540"/>
-    <mergeCell ref="W143:X143"/>
-    <mergeCell ref="W329:X329"/>
-    <mergeCell ref="W627:X627"/>
-    <mergeCell ref="W230:X230"/>
-    <mergeCell ref="W95:X95"/>
-    <mergeCell ref="W537:X537"/>
-    <mergeCell ref="W266:X266"/>
-    <mergeCell ref="W393:X393"/>
-    <mergeCell ref="W564:X564"/>
-    <mergeCell ref="W331:X331"/>
-    <mergeCell ref="W232:X232"/>
-    <mergeCell ref="W104:X104"/>
-    <mergeCell ref="W340:X340"/>
-    <mergeCell ref="W79:X79"/>
-    <mergeCell ref="W54:X54"/>
-    <mergeCell ref="W321:X321"/>
-    <mergeCell ref="W508:X508"/>
-    <mergeCell ref="W613:X613"/>
-    <mergeCell ref="W41:X41"/>
-    <mergeCell ref="W106:X106"/>
-    <mergeCell ref="U733:V733"/>
-    <mergeCell ref="W24:X24"/>
-    <mergeCell ref="W89:X89"/>
-    <mergeCell ref="W260:X260"/>
-    <mergeCell ref="W453:X453"/>
-    <mergeCell ref="W545:X545"/>
-    <mergeCell ref="W26:X26"/>
-    <mergeCell ref="W324:X324"/>
-    <mergeCell ref="W113:X113"/>
-    <mergeCell ref="W380:X380"/>
-    <mergeCell ref="W184:X184"/>
-    <mergeCell ref="W616:X616"/>
-    <mergeCell ref="W100:X100"/>
-    <mergeCell ref="W165:X165"/>
-    <mergeCell ref="W336:X336"/>
-    <mergeCell ref="W634:X634"/>
-    <mergeCell ref="W705:X705"/>
-    <mergeCell ref="T660:U660"/>
-    <mergeCell ref="W115:X115"/>
-    <mergeCell ref="W382:X382"/>
-    <mergeCell ref="U680:V680"/>
-    <mergeCell ref="W42:X42"/>
-    <mergeCell ref="W400:X400"/>
-    <mergeCell ref="W471:X471"/>
-    <mergeCell ref="W5:X5"/>
-    <mergeCell ref="W447:X447"/>
-    <mergeCell ref="W618:X618"/>
-    <mergeCell ref="W384:X384"/>
-    <mergeCell ref="W449:X449"/>
-    <mergeCell ref="W150:X150"/>
-    <mergeCell ref="W144:X144"/>
-    <mergeCell ref="W411:X411"/>
-    <mergeCell ref="W386:X386"/>
-    <mergeCell ref="W442:X442"/>
-    <mergeCell ref="W513:X513"/>
-    <mergeCell ref="W21:X21"/>
-    <mergeCell ref="W152:X152"/>
-    <mergeCell ref="W208:X208"/>
-    <mergeCell ref="W450:X450"/>
-    <mergeCell ref="W244:X244"/>
-    <mergeCell ref="W425:X425"/>
-    <mergeCell ref="W219:X219"/>
-    <mergeCell ref="W210:X210"/>
-    <mergeCell ref="W477:X477"/>
-    <mergeCell ref="W283:X283"/>
-    <mergeCell ref="W519:X519"/>
-    <mergeCell ref="W589:X589"/>
-    <mergeCell ref="W241:X241"/>
-    <mergeCell ref="W2:X2"/>
-    <mergeCell ref="W366:X366"/>
-    <mergeCell ref="W437:X437"/>
-    <mergeCell ref="W371:X371"/>
-    <mergeCell ref="W431:X431"/>
-    <mergeCell ref="W60:X60"/>
-    <mergeCell ref="W502:X502"/>
-    <mergeCell ref="W729:X729"/>
-    <mergeCell ref="W358:X358"/>
-    <mergeCell ref="W231:X231"/>
-    <mergeCell ref="W287:X287"/>
-    <mergeCell ref="W656:X656"/>
-    <mergeCell ref="W594:X594"/>
-    <mergeCell ref="W716:X716"/>
-    <mergeCell ref="W53:X53"/>
-    <mergeCell ref="W495:X495"/>
-    <mergeCell ref="W422:X422"/>
-    <mergeCell ref="W593:X593"/>
-    <mergeCell ref="W360:X360"/>
-    <mergeCell ref="W289:X289"/>
-    <mergeCell ref="W658:X658"/>
-    <mergeCell ref="W68:X68"/>
-    <mergeCell ref="W239:X239"/>
-    <mergeCell ref="W84:X84"/>
-    <mergeCell ref="W7:X7"/>
-    <mergeCell ref="W200:X200"/>
-    <mergeCell ref="U734:V734"/>
-    <mergeCell ref="W292:X292"/>
-    <mergeCell ref="W563:X563"/>
-    <mergeCell ref="W721:X721"/>
-    <mergeCell ref="W71:X71"/>
-    <mergeCell ref="W429:X429"/>
-    <mergeCell ref="W58:X58"/>
-    <mergeCell ref="W500:X500"/>
-    <mergeCell ref="W258:X258"/>
-    <mergeCell ref="W294:X294"/>
-    <mergeCell ref="W592:X592"/>
-    <mergeCell ref="W8:X8"/>
-    <mergeCell ref="W684:X684"/>
-    <mergeCell ref="W711:X711"/>
-    <mergeCell ref="W686:X686"/>
-    <mergeCell ref="W539:X539"/>
-    <mergeCell ref="W333:X333"/>
-    <mergeCell ref="W10:X10"/>
-    <mergeCell ref="W501:X501"/>
-    <mergeCell ref="W99:X99"/>
-    <mergeCell ref="W664:X664"/>
-    <mergeCell ref="W74:X74"/>
-    <mergeCell ref="T367:U367"/>
-    <mergeCell ref="W118:X118"/>
-    <mergeCell ref="W482:X482"/>
-    <mergeCell ref="W167:X167"/>
-    <mergeCell ref="W142:X142"/>
-    <mergeCell ref="W80:X80"/>
-    <mergeCell ref="W403:X403"/>
-    <mergeCell ref="W378:X378"/>
-    <mergeCell ref="W574:X574"/>
-    <mergeCell ref="T277:U277"/>
-    <mergeCell ref="W182:X182"/>
-    <mergeCell ref="W169:X169"/>
-    <mergeCell ref="W434:X434"/>
-    <mergeCell ref="W372:X372"/>
-    <mergeCell ref="W310:X310"/>
-    <mergeCell ref="W163:X163"/>
-    <mergeCell ref="W138:X138"/>
-    <mergeCell ref="W309:X309"/>
-    <mergeCell ref="W374:X374"/>
-    <mergeCell ref="W361:X361"/>
-    <mergeCell ref="W140:X140"/>
-    <mergeCell ref="W311:X311"/>
-    <mergeCell ref="W229:X229"/>
-    <mergeCell ref="W387:X387"/>
-    <mergeCell ref="W14:X14"/>
-    <mergeCell ref="W318:X318"/>
-    <mergeCell ref="W312:X312"/>
-    <mergeCell ref="W579:X579"/>
-    <mergeCell ref="W668:X668"/>
-    <mergeCell ref="W78:X78"/>
-    <mergeCell ref="W376:X376"/>
-    <mergeCell ref="W643:X643"/>
-    <mergeCell ref="W205:X205"/>
-    <mergeCell ref="W314:X314"/>
-    <mergeCell ref="W124:X124"/>
-    <mergeCell ref="W645:X645"/>
-    <mergeCell ref="W55:X55"/>
-    <mergeCell ref="W608:X608"/>
-    <mergeCell ref="W595:X595"/>
-    <mergeCell ref="W76:X76"/>
-    <mergeCell ref="W659:X659"/>
-    <mergeCell ref="W29:X29"/>
-    <mergeCell ref="W23:X23"/>
-    <mergeCell ref="W216:X216"/>
-    <mergeCell ref="W514:X514"/>
-    <mergeCell ref="W452:X452"/>
-    <mergeCell ref="W550:X550"/>
-    <mergeCell ref="W160:X160"/>
-    <mergeCell ref="W715:X715"/>
-    <mergeCell ref="W131:X131"/>
-    <mergeCell ref="W690:X690"/>
-    <mergeCell ref="W494:X494"/>
-    <mergeCell ref="W350:X350"/>
-    <mergeCell ref="W410:X410"/>
-    <mergeCell ref="W456:X456"/>
-    <mergeCell ref="W568:X568"/>
-    <mergeCell ref="W731:X731"/>
-    <mergeCell ref="W722:X722"/>
-    <mergeCell ref="W685:X685"/>
-    <mergeCell ref="W427:X427"/>
-    <mergeCell ref="W451:X451"/>
-    <mergeCell ref="W245:X245"/>
-    <mergeCell ref="W516:X516"/>
-    <mergeCell ref="W687:X687"/>
-    <mergeCell ref="W614:X614"/>
-    <mergeCell ref="W193:X193"/>
-    <mergeCell ref="W168:X168"/>
-    <mergeCell ref="W698:X698"/>
-    <mergeCell ref="W148:X148"/>
-    <mergeCell ref="W204:X204"/>
-    <mergeCell ref="W179:X179"/>
-    <mergeCell ref="W446:X446"/>
-    <mergeCell ref="W586:X586"/>
-    <mergeCell ref="W713:X713"/>
-    <mergeCell ref="W129:X129"/>
-    <mergeCell ref="W63:X63"/>
-    <mergeCell ref="W123:X123"/>
-    <mergeCell ref="W365:X365"/>
-    <mergeCell ref="W50:X50"/>
-    <mergeCell ref="W492:X492"/>
-    <mergeCell ref="W286:X286"/>
-    <mergeCell ref="W479:X479"/>
-    <mergeCell ref="W650:X650"/>
-    <mergeCell ref="W87:X87"/>
-    <mergeCell ref="W77:X77"/>
-    <mergeCell ref="W440:X440"/>
-    <mergeCell ref="W611:X611"/>
-    <mergeCell ref="W240:X240"/>
-    <mergeCell ref="W669:X669"/>
-    <mergeCell ref="W377:X377"/>
-    <mergeCell ref="W548:X548"/>
-    <mergeCell ref="W206:X206"/>
-    <mergeCell ref="W635:X635"/>
-    <mergeCell ref="W695:X695"/>
-    <mergeCell ref="W629:X629"/>
-    <mergeCell ref="W708:X708"/>
-    <mergeCell ref="W128:X128"/>
-    <mergeCell ref="W426:X426"/>
-    <mergeCell ref="W255:X255"/>
-    <mergeCell ref="W364:X364"/>
-    <mergeCell ref="W497:X497"/>
-    <mergeCell ref="W413:X413"/>
-    <mergeCell ref="W65:X65"/>
-    <mergeCell ref="W192:X192"/>
-    <mergeCell ref="W428:X428"/>
-    <mergeCell ref="W355:X355"/>
-    <mergeCell ref="W415:X415"/>
-    <mergeCell ref="W277:X277"/>
-    <mergeCell ref="W404:X404"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="W2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
